--- a/Comparacion de tiempos.xlsx
+++ b/Comparacion de tiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7789b221288dc1f1/Documentos/GitHub/sort-compare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="11_AD4D2F04E46CFB4ACB3E20A86552CEA2683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD0EF224-FB0A-4892-AE23-C8431B799E72}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="11_AD4D2F04E46CFB4ACB3E20A86552CEA2683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9BEC4FC-DA8D-4A3D-A116-7B9ACC182F09}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,9 +79,9 @@
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
     <numFmt numFmtId="166" formatCode="0.0000000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +91,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -299,6 +307,21 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -314,22 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,36 +634,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="18" t="s">
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="18" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="19"/>
-      <c r="P1" s="19"/>
-      <c r="Q1" s="19"/>
-      <c r="R1" s="19"/>
-      <c r="S1" s="20"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+      <c r="S1" s="35"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
+      <c r="A2" s="32"/>
       <c r="B2" s="2">
         <v>1</v>
       </c>
@@ -715,38 +723,38 @@
       <c r="A3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="23">
+      <c r="B3" s="18">
         <v>5.4836273193359299E-6</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="19">
         <v>5.7220458984375E-6</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="19">
         <v>5.00679016113281E-6</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="19">
         <v>4.5299530029296799E-6</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="20">
         <v>5.7220458984375E-6</v>
       </c>
-      <c r="G3" s="21">
+      <c r="G3" s="16">
         <f>AVERAGE(B3:F3)</f>
         <v>5.2928924560546839E-6</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="26">
         <v>1.6619682312011701E-2</v>
       </c>
-      <c r="I3" s="36">
+      <c r="I3" s="30">
         <v>1.5666246414184501E-2</v>
       </c>
-      <c r="J3" s="36">
+      <c r="J3" s="30">
         <v>1.4676809310912999E-2</v>
       </c>
-      <c r="K3" s="36">
+      <c r="K3" s="30">
         <v>1.5172004699707E-2</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="30">
         <v>1.52561664581298E-2</v>
       </c>
       <c r="M3" s="12">
@@ -780,35 +788,35 @@
       <c r="B4" s="8">
         <v>5.96046447753906E-6</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="9">
         <v>7.1525573730468699E-6</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="9">
         <v>6.1988830566406199E-6</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="9">
         <v>6.91413879394531E-6</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="21">
         <v>7.1525573730468699E-6</v>
       </c>
-      <c r="G4" s="21">
+      <c r="G4" s="16">
         <f t="shared" ref="G4:G8" si="0">AVERAGE(B4:F4)</f>
         <v>6.6757202148437458E-6</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="26">
         <v>1.5654802322387602E-2</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="30">
         <v>1.5982389450073201E-2</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="30">
         <v>1.52795314788818E-2</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="30">
         <v>1.5976905822753899E-2</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="30">
         <v>1.5918970108032199E-2</v>
       </c>
       <c r="M4" s="12">
@@ -842,35 +850,35 @@
       <c r="B5" s="8">
         <v>6.91413879394531E-6</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="9">
         <v>1.5497207641601502E-5</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="9">
         <v>6.67572021484375E-6</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="9">
         <v>6.67572021484375E-6</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="21">
         <v>1.52587890625E-5</v>
       </c>
-      <c r="G5" s="21">
+      <c r="G5" s="16">
         <f t="shared" si="0"/>
         <v>1.0204315185546861E-5</v>
       </c>
-      <c r="H5" s="36">
+      <c r="H5" s="30">
         <v>3.4366607666015597E-2</v>
       </c>
-      <c r="I5" s="36">
+      <c r="I5" s="30">
         <v>3.2799720764160101E-2</v>
       </c>
-      <c r="J5" s="36">
+      <c r="J5" s="30">
         <v>3.1974077224731397E-2</v>
       </c>
-      <c r="K5" s="36">
+      <c r="K5" s="30">
         <v>3.2957792282104402E-2</v>
       </c>
-      <c r="L5" s="36">
+      <c r="L5" s="30">
         <v>4.3374538421630797E-2</v>
       </c>
       <c r="M5" s="12">
@@ -904,54 +912,54 @@
       <c r="B6" s="8">
         <v>1.28746032714843E-5</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="9">
         <v>1.2397766113281199E-5</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="9">
         <v>1.71661376953125E-5</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="9">
         <v>1.38282775878906E-5</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="21">
         <v>1.31130218505859E-5</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="16">
         <f t="shared" si="0"/>
         <v>1.3875961303710899E-5</v>
       </c>
-      <c r="H6" s="36">
+      <c r="H6" s="30">
         <v>1.5618801116943301E-3</v>
       </c>
-      <c r="I6" s="36">
+      <c r="I6" s="30">
         <v>1.3227462768554601E-3</v>
       </c>
-      <c r="J6" s="36">
+      <c r="J6" s="30">
         <v>1.32632255554199E-3</v>
       </c>
-      <c r="K6" s="36">
+      <c r="K6" s="30">
         <v>1.2161731719970701E-3</v>
       </c>
-      <c r="L6" s="36">
+      <c r="L6" s="30">
         <v>1.2781620025634701E-3</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="1"/>
         <v>1.3410568237304638E-3</v>
       </c>
-      <c r="N6" s="35">
+      <c r="N6" s="29">
         <v>9.2754602432250893E-2</v>
       </c>
-      <c r="O6" s="35">
+      <c r="O6" s="29">
         <v>0.10171556472778299</v>
       </c>
-      <c r="P6" s="35">
+      <c r="P6" s="29">
         <v>9.4923019409179604E-2</v>
       </c>
-      <c r="Q6" s="35">
+      <c r="Q6" s="29">
         <v>9.4741582870483398E-2</v>
       </c>
-      <c r="R6" s="35">
+      <c r="R6" s="29">
         <v>9.6983671188354395E-2</v>
       </c>
       <c r="S6" s="10">
@@ -966,54 +974,54 @@
       <c r="B7" s="8">
         <v>4.4898986816406198E-3</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C7" s="9">
         <v>7.62939453125E-6</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="9">
         <v>5.2452087402343699E-6</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="9">
         <v>5.7220458984375E-6</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="21">
         <v>5.96046447753906E-6</v>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="16">
         <f t="shared" si="0"/>
         <v>9.028911590576161E-4</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="26">
         <v>7.09295272827148E-4</v>
       </c>
-      <c r="I7" s="36">
+      <c r="I7" s="30">
         <v>2.4223327636718701E-4</v>
       </c>
-      <c r="J7" s="36">
+      <c r="J7" s="30">
         <v>2.4890899658203098E-4</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="30">
         <v>2.3365020751953101E-4</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="30">
         <v>2.1934509277343701E-4</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" si="1"/>
         <v>3.3068656921386686E-4</v>
       </c>
-      <c r="N7" s="29">
+      <c r="N7" s="23">
         <v>1.67205333709716E-2</v>
       </c>
-      <c r="O7" s="35">
+      <c r="O7" s="29">
         <v>2.0035505294799801E-2</v>
       </c>
-      <c r="P7" s="35">
+      <c r="P7" s="29">
         <v>1.7355442047119099E-2</v>
       </c>
-      <c r="Q7" s="35">
+      <c r="Q7" s="29">
         <v>1.9801378250122001E-2</v>
       </c>
-      <c r="R7" s="35">
+      <c r="R7" s="29">
         <v>2.09097862243652E-2</v>
       </c>
       <c r="S7" s="10">
@@ -1037,45 +1045,45 @@
       <c r="E8" s="15">
         <v>2.5033950805664002E-5</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="22">
         <v>2.5272369384765601E-5</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="17">
         <f t="shared" si="0"/>
         <v>1.9264221191406178E-5</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="27">
         <v>9.6654891967773405E-4</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="28">
         <v>9.3674659729003895E-4</v>
       </c>
-      <c r="J8" s="34">
+      <c r="J8" s="28">
         <v>9.2482566833495996E-4</v>
       </c>
-      <c r="K8" s="34">
+      <c r="K8" s="28">
         <v>9.3317031860351497E-4</v>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="28">
         <v>9.3102455139160102E-4</v>
       </c>
       <c r="M8" s="13">
         <f t="shared" si="1"/>
         <v>9.3846321105956984E-4</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="24">
         <v>7.0123672485351493E-2</v>
       </c>
-      <c r="O8" s="31">
+      <c r="O8" s="25">
         <v>7.1588277816772405E-2</v>
       </c>
-      <c r="P8" s="31">
+      <c r="P8" s="25">
         <v>7.3649644851684501E-2</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="25">
         <v>7.2632312774658203E-2</v>
       </c>
-      <c r="R8" s="31">
+      <c r="R8" s="25">
         <v>7.4522256851196206E-2</v>
       </c>
       <c r="S8" s="11">
@@ -1084,29 +1092,19 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="9">
-        <v>7.0123672485351493E-2</v>
-      </c>
+      <c r="B10" s="36"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="9">
-        <v>7.1588277816772405E-2</v>
-      </c>
+      <c r="B11" s="36"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
-        <v>7.3649644851684501E-2</v>
-      </c>
+      <c r="B12" s="36"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="9">
-        <v>7.2632312774658203E-2</v>
-      </c>
+      <c r="B13" s="36"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="9">
-        <v>7.4522256851196206E-2</v>
-      </c>
+      <c r="B14" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Comparacion de tiempos.xlsx
+++ b/Comparacion de tiempos.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7789b221288dc1f1/Documentos/GitHub/sort-compare/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="11_AD4D2F04E46CFB4ACB3E20A86552CEA2683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9BEC4FC-DA8D-4A3D-A116-7B9ACC182F09}"/>
+  <xr:revisionPtr revIDLastSave="305" documentId="11_AD4D2F04E46CFB4ACB3E20A86552CEA2683EDF1F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{332A164D-D2AD-4B18-9CEF-434A8E639EF7}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcCompleted="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -322,6 +322,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -337,7 +338,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -353,6 +353,4009 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-HN"/>
+              <a:t>Graficas</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-HN" baseline="0"/>
+              <a:t> de tiempo para Arrays Pequeños</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Series1</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$B$3:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.4836273193359299E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.96046447753906E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.91413879394531E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.28746032714843E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4.4898986816406198E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0251998901367099E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Series2</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$C$3:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.7220458984375E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1525573730468699E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.5497207641601502E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2397766113281199E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.62939453125E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.3603439331054599E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Series3</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$D$3:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.00679016113281E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.1988830566406199E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.67572021484375E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.71661376953125E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.2452087402343699E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.2159347534179599E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>Series4</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$E$3:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>4.5299530029296799E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.91413879394531E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.67572021484375E-6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.38282775878906E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.7220458984375E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5033950805664002E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:v>Series5</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$F$3:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.7220458984375E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.1525573730468699E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.52587890625E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.31130218505859E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5.96046447753906E-6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.5272369384765601E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$G$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Medio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$G$3:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>5.2928924560546839E-6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6.6757202148437458E-6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.0204315185546861E-5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3875961303710899E-5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.028911590576161E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.9264221191406178E-5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-2291-46DD-A3F1-EC7823C27F52}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="387807664"/>
+        <c:axId val="387802384"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="387807664"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="387802384"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="387802384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="387807664"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-HN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-HN"/>
+              <a:t>Gráficas</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-HN" baseline="0"/>
+              <a:t> de tiempo para Arryas Medianos</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$H$3:$H$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.6619682312011701E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5654802322387602E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.4366607666015597E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5618801116943301E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.09295272827148E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.6654891967773405E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$I$3:$I$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.5666246414184501E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5982389450073201E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2799720764160101E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3227462768554601E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4223327636718701E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.3674659729003895E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$J$3:$J$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.4676809310912999E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.52795314788818E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.1974077224731397E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.32632255554199E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.4890899658203098E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.2482566833495996E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$K$3:$K$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.5172004699707E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5976905822753899E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.2957792282104402E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2161731719970701E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.3365020751953101E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.3317031860351497E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$L$3:$L$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.52561664581298E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.5918970108032199E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4.3374538421630797E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.2781620025634701E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2.1934509277343701E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.3102455139160102E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Medio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$M$3:$M$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.000000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1.5478181838989202E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.576251983642574E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3.5094547271728463E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.3410568237304638E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.3068656921386686E-4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.3846321105956984E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-5851-45C0-BDAA-6CF3FEDE33EC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="722226224"/>
+        <c:axId val="722226704"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="722226224"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="722226704"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="722226704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="722226224"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-HN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-HN"/>
+              <a:t>Gráficas</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-HN" baseline="0"/>
+              <a:t> de tiempo para Arrays Extra Grandes</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$N$3:$N$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>48.940302848815897</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>41.923101902008</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>128.87342905998199</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>9.2754602432250893E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>1.67205333709716E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>7.0123672485351493E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$O$3:$O$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>63.7226753234863</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>54.918815374374297</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>164.19914364814699</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>0.10171556472778299</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>2.0035505294799801E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>7.1588277816772405E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$P$3:$P$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>52.856142282485898</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48.876542329788201</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>144.80951833724899</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>9.4923019409179604E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>1.7355442047119099E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>7.3649644851684501E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$Q$3:$Q$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>46.245748519897397</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42.141280651092501</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>136.99730420112601</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>9.4741582870483398E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>1.9801378250122001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>7.2632312774658203E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$R$3:$R$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>54.6687362194061</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42.7264821529388</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>134.34915542602499</c:v>
+                </c:pt>
+                <c:pt idx="3" formatCode="0.0000">
+                  <c:v>9.6983671188354395E-2</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="0.0000">
+                  <c:v>2.09097862243652E-2</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="0.0000">
+                  <c:v>7.4522256851196206E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$S$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Medio</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Hoja1!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Insertion Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Bubble Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Heap Sort </c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$S$3:$S$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00000</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>53.286721038818314</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>46.117244482040363</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>141.84571013450577</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.622368812561026E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.8964529037475541E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.250323295593257E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-4CAD-4DFA-A1A9-416791ECA317}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1062617439"/>
+        <c:axId val="1062625599"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1062617439"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1062625599"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1062625599"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-HN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1062617439"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-HN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-HN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{292B8D95-B17E-1034-D204-E22E183C9196}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>619125</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Gráfico 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C8E49C4-35D3-C7FB-4003-EBC2CF4DF5E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>714375</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="7" name="Gráfico 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03731C35-81FA-1EE1-12E0-2CE04DB0AC68}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,36 +4637,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="33" t="s">
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="33" t="s">
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="34"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="34"/>
-      <c r="R1" s="34"/>
-      <c r="S1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="36"/>
     </row>
     <row r="2" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="2">
         <v>1</v>
       </c>
@@ -1092,19 +5095,19 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B10" s="36"/>
+      <c r="B10" s="31"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
+      <c r="B11" s="31"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B12" s="36"/>
+      <c r="B12" s="31"/>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B13" s="36"/>
+      <c r="B13" s="31"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="B14" s="36"/>
+      <c r="B14" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1114,5 +5117,6 @@
     <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>